--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_252_Tromelin_Isl_France.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_252_Tromelin_Isl_France.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R90703dde60304cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4d612d623dd747da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R9533ae495f274b53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R574394c37b054964"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6afb52492b044c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R111da96622874b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2cda0a61e4ff4907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R87eba9b575aa4133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R21655b3a807349a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R58dea6f68a10428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9468932ce6b34958"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2deba9c8970c401e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ252CommercialTable" displayName="EEZ252CommercialTable" ref="A1:O5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O5"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ252CommercialTable" displayName="EEZ252CommercialTable" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E5"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ252FunctionalTable" displayName="EEZ252FunctionalTable" ref="A1:O5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O5"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ252FunctionalTable" displayName="EEZ252FunctionalTable" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E5"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ252ValidationTable" displayName="EEZ252ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ252ValidationTable" displayName="EEZ252ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -1766,7 +1720,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34426a25e9bf4bee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85079eaf54e74b60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1776,20 +1730,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1797,282 +1741,98 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.6842206262</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.280547504946</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>190.7864402760989</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.6842206262</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>190.80673140859244</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$17,A2,'Species'!$U$2:$U$17))</x:f>
-        <x:v>130.55390124756232</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.280547504946</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>190.7864402760989</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>130.5400176361813</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0.013883611381032779</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0001063552130025</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00010635521300239744</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5.6399508169</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.356039703409457</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2270.072373501012</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5.6399508169</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2300.238375315914</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$17,A3,'Species'!$U$2:$U$17))</x:f>
-        <x:v>12973.231303927718</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.356039703409457</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2270.072373501012</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>12803.096537349154</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>170.13476657856336</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0132885639096954</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.013288563909695341</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.1265830245</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.271030916195244</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1866.512557852724</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.1265830245</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1971.2378478256778</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$17,A4,'Species'!$U$2:$U$17))</x:f>
-        <x:v>249.52524878664505</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.271030916195244</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1866.512557852724</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>236.26880484022905</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>13.256443946415999</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0561074660507144</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.05610746605071432</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>13.607216793400001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.290816179711591</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1953.512433466168</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>13.607216793400001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2004.580367465276</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$17,A5,'Species'!$U$2:$U$17))</x:f>
-        <x:v>27276.759639893447</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.290816179711591</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1953.512433466168</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>26581.867190776542</x:v>
       </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>694.8924491169055</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0261415966052987</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.02614159660529872</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G5">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O5">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a580b4cae3c413c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc982550783d04e89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2082,20 +1842,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2103,282 +1853,98 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9.7552499356</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.377969298877037</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2387.6424898481846</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9.7552499356</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2435.0917402554073</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$17,A2,'Species'!$U$2:$U$17))</x:f>
-        <x:v>23754.928542306654</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.377969298877037</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2387.6424898481846</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>23292.049245327325</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>462.8792969793285</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.019872845540724</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.019872845540724066</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.1265830245</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.271030916195244</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1866.512557852724</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.1265830245</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1971.2378478256778</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$17,A3,'Species'!$U$2:$U$17))</x:f>
-        <x:v>249.52524878664505</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.271030916195244</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1866.512557852724</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>236.26880484022905</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>13.256443946415999</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0561074660507144</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.05610746605071432</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.6788689951</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>190.54607179632464</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.6788689951</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$17,A4,'Species'!$U$2:$U$17))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>129.35582028062336</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>129.35582028062336</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>9.4972693058</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.239498492511307</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1735.7952377057036</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>9.4972693058</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1736.947742695593</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$17,A5,'Species'!$U$2:$U$17))</x:f>
-        <x:v>16496.26048248145</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.239498492511307</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1735.7952377057036</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>16485.314832216194</x:v>
       </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>10.945650265257427</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0006639636777739</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0006639636777738114</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G5">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O5">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8762c88df9f64edd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8987450aa3be4081"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2553,7 +2119,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -2652,7 +2218,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>40630.07009385537</x:v>
+        <x:v>39751.77255060211</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2666,7 +2232,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>40630.07009385537</x:v>
+        <x:v>40142.98870266437</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2680,7 +2246,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-878.2975432532621</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2694,7 +2260,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-487.0813911910009</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2705,9 +2271,9 @@
         <x:v>EEZ_252</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -2719,47 +2285,19 @@
         <x:v>EEZ_252</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_252</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_252</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8eb10df2152642d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c709a3e08064f1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2806,7 +2344,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
